--- a/Lab_4/data/partB/param_optimization_process/v200_k40_s200_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v200_k40_s200_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>8</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -594,13 +594,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,22 +646,22 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -677,46 +677,46 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -735,40 +735,40 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N6" t="n">
-        <v>11</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -787,40 +787,40 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,22 +842,22 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -891,40 +891,40 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
         <v>7</v>
       </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -958,19 +958,19 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -995,40 +995,40 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1062,22 +1062,22 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1090,13 +1090,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1105,19 +1105,19 @@
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>63</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1154,37 +1154,37 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,22 +1246,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1270,25 +1270,25 @@
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19372,7 +19372,7 @@
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20188,7 @@
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20596,7 +20596,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20800,7 +20800,7 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22126,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22211,7 +22211,7 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23214,7 +23214,7 @@
       </c>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23265,7 +23265,7 @@
       </c>
       <c r="C1292" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24132,7 +24132,7 @@
       </c>
       <c r="C1343" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24608,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25271,7 +25271,7 @@
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26784,7 +26784,7 @@
       </c>
       <c r="C1499" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
